--- a/data/availability/projects/al-qamzi-developments/seazen.xlsx
+++ b/data/availability/projects/al-qamzi-developments/seazen.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for seazen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -554,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -935,7 +945,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -959,7 +969,6 @@
       <c r="G2" t="n">
         <v>54</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -970,7 +979,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1016,7 +1025,6 @@
       <c r="G3" t="n">
         <v>63</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1027,7 +1035,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1073,7 +1081,6 @@
       <c r="G4" t="n">
         <v>86</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1084,7 +1091,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1130,7 +1137,6 @@
       <c r="G5" t="n">
         <v>170</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1187,7 +1193,6 @@
       <c r="G6" t="n">
         <v>205</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1244,7 +1249,6 @@
       <c r="G7" t="n">
         <v>235</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
